--- a/artfynd/A 69061-2021 artfynd.xlsx
+++ b/artfynd/A 69061-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,57 +680,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132012536</v>
+        <v>136798682</v>
       </c>
       <c r="B2" t="n">
-        <v>99195</v>
+        <v>8463</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lintjärnen, Dlr</t>
+          <t>Born, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>514113</v>
+        <v>514058</v>
       </c>
       <c r="R2" t="n">
-        <v>6757269</v>
+        <v>6757263</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,22 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,16 +775,137 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136798682</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>132012536</v>
+      </c>
+      <c r="B3" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Lintjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>514113</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6757269</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Irina Röjås</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Irina Röjås</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/132012536</t>
         </is>
@@ -802,6 +914,7 @@
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 69061-2021 artfynd.xlsx
+++ b/artfynd/A 69061-2021 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136798682</v>
       </c>
       <c r="B2" t="n">
-        <v>8463</v>
+        <v>8464</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 69061-2021 artfynd.xlsx
+++ b/artfynd/A 69061-2021 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136798682</v>
       </c>
       <c r="B2" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
